--- a/output/pdf_financials_xlsx/PBL.xlsx
+++ b/output/pdf_financials_xlsx/PBL.xlsx
@@ -4355,40 +4355,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.456</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.384</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.917</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.965</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>12.698</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.705</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>-1.579</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>8.913</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>24.127</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>27.762</v>
       </c>
     </row>
     <row r="93">
@@ -8410,7 +8410,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.219</v>
       </c>

--- a/output/pdf_financials_xlsx/PBL.xlsx
+++ b/output/pdf_financials_xlsx/PBL.xlsx
@@ -1837,40 +1837,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>7.774</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>6.212</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>7.587</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.603</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>11.174</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>7.448</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.517</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.479</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>8.411</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>22.36</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="35">
@@ -1923,40 +1923,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>7.774</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>6.212</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>7.587</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.603</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>11.174</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>7.448</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.517</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.479</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>8.411</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>22.36</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="37">
@@ -2439,40 +2439,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>9.786</v>
+        <v>2.012</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>9.561999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>15.362</v>
+        <v>7.775</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>14.14</v>
+        <v>6.64</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>17.714</v>
+        <v>12.111</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>30.554</v>
+        <v>19.38</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>32.872</v>
+        <v>25.424</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>34.807</v>
+        <v>31.29</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>43.491</v>
+        <v>42.012</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>47.018</v>
+        <v>38.607</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>84.318</v>
+        <v>61.958</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>95.607</v>
+        <v>67.14700000000001</v>
       </c>
     </row>
     <row r="49">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/PBL.xlsx
+++ b/output/pdf_financials_xlsx/PBL.xlsx
@@ -14332,7 +14332,11 @@
           <t>Additions to intangible assets (note 12)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -15840,7 +15844,11 @@
           <t>Additions to intangible assets (note 11)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -16408,7 +16416,11 @@
           <t>Additions to intangible assets (note 11)</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -19914,7 +19926,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E192" s="5" t="n">
         <v>-3.766</v>
       </c>
